--- a/data/Escenarios_DCH/Carga_on_board_variable_3estaciones/elmo_data.xlsx
+++ b/data/Escenarios_DCH/Carga_on_board_variable_3estaciones/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH\Carga_on_board_variable_3estaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC0D3B6-DC4D-47EC-BA08-C3A667B9B931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596ADBAF-4DA3-43A8-A362-6AD566CE9E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -3446,19 +3446,19 @@
         <v>379</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -3469,19 +3469,19 @@
         <v>387</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -3492,19 +3492,19 @@
         <v>388</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>215756</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>5000</v>
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
